--- a/AAII_Financials/Quarterly/IFBD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IFBD_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="92">
   <si>
     <t>IFBD</t>
   </si>
@@ -656,7 +656,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -670,185 +670,211 @@
     <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44012</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>43830</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>43646</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>2900</v>
+        <v>300</v>
       </c>
       <c r="E8" s="3">
-        <v>2600</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
         <v>5200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>4500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>14500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>6200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>18200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>9400</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1900</v>
-      </c>
-      <c r="E9" s="3">
-        <v>1700</v>
-      </c>
-      <c r="F9" s="3">
+        <v>100</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H9" s="3">
         <v>3600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>3700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>4700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>2200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>8000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>4600</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1000</v>
-      </c>
-      <c r="E10" s="3">
-        <v>900</v>
-      </c>
-      <c r="F10" s="3">
+        <v>200</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" s="3">
         <v>1600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>9800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>4000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>10200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>4800</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,49 +890,57 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3">
         <v>900</v>
       </c>
-      <c r="E12" s="3">
-        <v>2400</v>
-      </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="3">
         <v>1500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>1700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>1900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>1200</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,29 +980,35 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>2600</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>1300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>2400</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -981,14 +1021,20 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,8 +1074,14 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,90 +1094,104 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>10100</v>
+        <v>2600</v>
       </c>
       <c r="E17" s="3">
-        <v>9800</v>
+        <v>900</v>
       </c>
       <c r="F17" s="3">
+        <v>500</v>
+      </c>
+      <c r="G17" s="3">
+        <v>400</v>
+      </c>
+      <c r="H17" s="3">
         <v>13200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>10900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>10200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>4500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>12200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>7100</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-7200</v>
+        <v>-2300</v>
       </c>
       <c r="E18" s="3">
-        <v>-7200</v>
+        <v>-900</v>
       </c>
       <c r="F18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H18" s="3">
         <v>-8000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-6400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>4300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>1700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>6000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>2300</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,40 +1207,42 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
-        <v>-500</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H20" s="3">
         <v>500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>200</v>
-      </c>
-      <c r="I20" s="3">
-        <v>100</v>
       </c>
       <c r="J20" s="3">
         <v>200</v>
       </c>
       <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="L20" s="3">
+        <v>200</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
@@ -1182,131 +1250,155 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="E21" s="3">
-        <v>-7100</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="3">
+        <v>400</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="3">
         <v>5000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>2000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>6400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>2400</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1300</v>
+        <v>700</v>
       </c>
       <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>300</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
+        <v>200</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="L22" s="3">
+        <v>400</v>
+      </c>
+      <c r="M22" s="3">
         <v>300</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3">
-        <v>200</v>
-      </c>
-      <c r="I22" s="3">
-        <v>100</v>
-      </c>
-      <c r="J22" s="3">
-        <v>400</v>
-      </c>
-      <c r="K22" s="3">
-        <v>300</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-8400</v>
+        <v>-20700</v>
       </c>
       <c r="E23" s="3">
-        <v>-7800</v>
+        <v>-800</v>
       </c>
       <c r="F23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H23" s="3">
         <v>-7900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-6200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>4300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>5800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>2000</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1317,28 +1409,28 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>300</v>
-      </c>
-      <c r="I24" s="3">
-        <v>100</v>
-      </c>
-      <c r="J24" s="3">
-        <v>700</v>
       </c>
       <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
+      <c r="L24" s="3">
+        <v>700</v>
+      </c>
+      <c r="M24" s="3">
+        <v>100</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
@@ -1346,8 +1438,14 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,90 +1485,108 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-8400</v>
+        <v>-20700</v>
       </c>
       <c r="E26" s="3">
-        <v>-7800</v>
+        <v>-800</v>
       </c>
       <c r="F26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H26" s="3">
         <v>-8000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-6300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>4100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>1600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>5100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>2000</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-7500</v>
+        <v>-20700</v>
       </c>
       <c r="E27" s="3">
-        <v>-7800</v>
+        <v>-500</v>
       </c>
       <c r="F27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H27" s="3">
         <v>-7900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-5900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>4000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>1500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>4800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1800</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,31 +1626,37 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>22700</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>-4100</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
+        <v>-6700</v>
       </c>
       <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+        <v>-6900</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1551,8 +1673,14 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1720,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,40 +1767,46 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
-        <v>500</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>400</v>
+      </c>
+      <c r="H32" s="3">
         <v>-500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-100</v>
       </c>
       <c r="J32" s="3">
         <v>-200</v>
       </c>
       <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
@@ -1674,49 +1814,61 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F33" s="3">
         <v>-7500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-7800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-7900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-5900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>4000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>1500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>4800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1800</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,95 +1908,113 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F35" s="3">
         <v>-7500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-7800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-7900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-5900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>4000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>1500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>4800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1800</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44012</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>43830</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>43646</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +2030,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,35 +2049,37 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
+        <v>200</v>
+      </c>
+      <c r="G41" s="3">
         <v>1400</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J41" s="3">
         <v>1700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1200</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1918,23 +2092,29 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>6700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>6700</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1947,11 +2127,11 @@
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="L42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -1959,35 +2139,41 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>500</v>
+        <v>5400</v>
       </c>
       <c r="E43" s="3">
+        <v>25000</v>
+      </c>
+      <c r="F43" s="3">
+        <v>14400</v>
+      </c>
+      <c r="G43" s="3">
         <v>3000</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3">
         <v>4200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>4800</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2000,8 +2186,14 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2041,35 +2233,41 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>5100</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F45" s="3">
+        <v>6500</v>
+      </c>
+      <c r="G45" s="3">
         <v>1100</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>1400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2082,35 +2280,41 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>13400</v>
+        <v>5500</v>
       </c>
       <c r="E46" s="3">
+        <v>32900</v>
+      </c>
+      <c r="F46" s="3">
+        <v>27400</v>
+      </c>
+      <c r="G46" s="3">
         <v>12300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>20400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>27100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>7300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>6100</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2123,8 +2327,14 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2164,35 +2374,41 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="3">
         <v>200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>300</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3">
         <v>2200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>2000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2205,35 +2421,41 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F49" s="3">
         <v>3000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>5900</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="H49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J49" s="3">
         <v>5200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>2900</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2246,8 +2468,14 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2515,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,35 +2562,41 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>52200</v>
       </c>
       <c r="E52" s="3">
         <v>200</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="F52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="G52" s="3">
+        <v>200</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3">
         <v>1200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1000</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2369,8 +2609,14 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,35 +2656,41 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>16600</v>
+        <v>57700</v>
       </c>
       <c r="E54" s="3">
+        <v>33100</v>
+      </c>
+      <c r="F54" s="3">
+        <v>30600</v>
+      </c>
+      <c r="G54" s="3">
         <v>18700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>28500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>33100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>16000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>12000</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2451,8 +2703,14 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2726,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,35 +2745,37 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>100</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F57" s="3">
         <v>3200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3300</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3">
         <v>600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2526,35 +2788,41 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F58" s="3">
         <v>3500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>3600</v>
       </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3">
         <v>3100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2800</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2567,35 +2835,41 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3300</v>
+        <v>0</v>
       </c>
       <c r="E59" s="3">
+        <v>24300</v>
+      </c>
+      <c r="F59" s="3">
+        <v>26800</v>
+      </c>
+      <c r="G59" s="3">
         <v>3700</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3">
         <v>3900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>3200</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2608,35 +2882,41 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>10100</v>
+        <v>100</v>
       </c>
       <c r="E60" s="3">
+        <v>24300</v>
+      </c>
+      <c r="F60" s="3">
+        <v>24100</v>
+      </c>
+      <c r="G60" s="3">
         <v>10600</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J60" s="3">
         <v>7500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6600</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2649,8 +2929,14 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2658,14 +2944,14 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>100</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
@@ -2690,8 +2976,14 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2699,26 +2991,26 @@
         <v>0</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3">
         <v>300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>300</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2731,8 +3023,14 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +3070,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +3117,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,35 +3164,41 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>10100</v>
+        <v>100</v>
       </c>
       <c r="E66" s="3">
+        <v>26100</v>
+      </c>
+      <c r="F66" s="3">
+        <v>24100</v>
+      </c>
+      <c r="G66" s="3">
         <v>11500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>13400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>11000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>8100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>7100</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2895,8 +3211,14 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3234,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3277,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3324,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3035,8 +3371,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,35 +3418,41 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-27600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-20100</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3">
         <v>1500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-1000</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3117,8 +3465,14 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3512,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3559,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,35 +3606,41 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>57600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F76" s="3">
         <v>6600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>7200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>15100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>22200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>7900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>4900</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3281,8 +3653,14 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,95 +3700,113 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44012</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>43830</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>43646</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F81" s="3">
         <v>-7500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-7800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-7900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-5900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>4000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>1500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>4800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1800</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,35 +3822,37 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3">
         <v>800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>600</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3">
         <v>500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>200</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3467,8 +3865,14 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +3912,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +3959,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +4006,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +4053,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,35 +4100,41 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-4000</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3">
         <v>1500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1200</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3713,8 +4147,14 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,8 +4170,10 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3759,11 +4201,11 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
@@ -3771,8 +4213,14 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4260,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,35 +4307,41 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-45400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-5300</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3">
         <v>-3200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-900</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3894,8 +4354,14 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,8 +4377,10 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3952,8 +4420,14 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4467,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4514,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,35 +4561,41 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>45700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F100" s="3">
         <v>6300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-700</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3">
         <v>-200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4116,34 +4608,40 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>100</v>
+      </c>
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
@@ -4157,35 +4655,41 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-4900</v>
       </c>
-      <c r="F102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H102" s="3">
+      <c r="H102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J102" s="3">
         <v>-1800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-2300</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4196,6 +4700,12 @@
         <v>3</v>
       </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IFBD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IFBD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="92">
   <si>
     <t>IFBD</t>
   </si>
@@ -656,225 +656,250 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44377</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44196</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44012</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>43830</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43646</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
-        <v>300</v>
+      <c r="D8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E8" s="3">
         <v>0</v>
       </c>
       <c r="F8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>5200</v>
-      </c>
-      <c r="I8" s="3">
+        <v>100</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3">
         <v>4500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>14500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>6200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>18200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>9400</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
         <v>100</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3">
-        <v>3600</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="G9" s="3">
+        <v>100</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K9" s="3">
         <v>3700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>4700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>2200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>8000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>4600</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>200</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>100</v>
+      </c>
+      <c r="G10" s="3">
+        <v>100</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" s="3">
         <v>800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>9800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>4000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>10200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>4800</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,8 +917,10 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -903,44 +930,50 @@
       <c r="E12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="3">
-        <v>900</v>
+      <c r="F12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M12" s="3">
+        <v>700</v>
+      </c>
+      <c r="N12" s="3">
         <v>1500</v>
       </c>
-      <c r="I12" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J12" s="3">
-        <v>1900</v>
-      </c>
-      <c r="K12" s="3">
-        <v>700</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1500</v>
-      </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1200</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,35 +1019,41 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>2400</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1027,14 +1066,20 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1045,19 +1090,19 @@
         <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1080,8 +1125,14 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,102 +1147,116 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2600</v>
+        <v>400</v>
       </c>
       <c r="E17" s="3">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="F17" s="3">
-        <v>500</v>
+        <v>1300</v>
       </c>
       <c r="G17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H17" s="3">
         <v>400</v>
       </c>
-      <c r="H17" s="3">
-        <v>13200</v>
-      </c>
       <c r="I17" s="3">
+        <v>400</v>
+      </c>
+      <c r="J17" s="3">
+        <v>200</v>
+      </c>
+      <c r="K17" s="3">
         <v>10900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>10200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>12200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>7100</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-2300</v>
+        <v>-400</v>
       </c>
       <c r="E18" s="3">
-        <v>-900</v>
+        <v>-400</v>
       </c>
       <c r="F18" s="3">
-        <v>-500</v>
+        <v>-1200</v>
       </c>
       <c r="G18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="H18" s="3">
         <v>-400</v>
       </c>
-      <c r="H18" s="3">
-        <v>-8000</v>
-      </c>
       <c r="I18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K18" s="3">
         <v>-6400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>4300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>1700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>6000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>2300</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,46 +1274,48 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-17700</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="G20" s="3">
-        <v>-400</v>
+        <v>8800</v>
       </c>
       <c r="H20" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>200</v>
-      </c>
-      <c r="J20" s="3">
-        <v>200</v>
-      </c>
-      <c r="K20" s="3">
-        <v>100</v>
       </c>
       <c r="L20" s="3">
         <v>200</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="N20" s="3">
+        <v>200</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
@@ -1256,187 +1323,211 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-400</v>
       </c>
       <c r="F21" s="3">
-        <v>400</v>
+        <v>-9800</v>
       </c>
       <c r="G21" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="H21" s="3">
         <v>-200</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
+      <c r="I21" s="3">
+        <v>-200</v>
       </c>
       <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
         <v>5000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>2000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>6400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>2400</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>700</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F22" s="3">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
+        <v>400</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
+        <v>600</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
+        <v>200</v>
+      </c>
+      <c r="M22" s="3">
+        <v>100</v>
+      </c>
+      <c r="N22" s="3">
+        <v>400</v>
+      </c>
+      <c r="O22" s="3">
         <v>300</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3">
-        <v>200</v>
-      </c>
-      <c r="K22" s="3">
-        <v>100</v>
-      </c>
-      <c r="L22" s="3">
-        <v>400</v>
-      </c>
-      <c r="M22" s="3">
-        <v>300</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-20700</v>
+        <v>-400</v>
       </c>
       <c r="E23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J23" s="3">
         <v>-800</v>
       </c>
-      <c r="F23" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-900</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-7900</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-6200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>4300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>1700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>5800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>2000</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>100</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>300</v>
-      </c>
-      <c r="K24" s="3">
-        <v>100</v>
-      </c>
-      <c r="L24" s="3">
-        <v>700</v>
       </c>
       <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
+      <c r="N24" s="3">
+        <v>700</v>
+      </c>
+      <c r="O24" s="3">
+        <v>100</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
@@ -1444,8 +1535,14 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,102 +1588,120 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-20700</v>
+        <v>-400</v>
       </c>
       <c r="E26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J26" s="3">
         <v>-800</v>
       </c>
-      <c r="F26" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-900</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-8000</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-6300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>4100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>5100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>2000</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-20700</v>
+        <v>-400</v>
       </c>
       <c r="E27" s="3">
-        <v>-500</v>
+        <v>-400</v>
       </c>
       <c r="F27" s="3">
-        <v>-800</v>
+        <v>1000</v>
       </c>
       <c r="G27" s="3">
-        <v>-800</v>
+        <v>1000</v>
       </c>
       <c r="H27" s="3">
-        <v>-7900</v>
+        <v>-2300</v>
       </c>
       <c r="I27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="K27" s="3">
         <v>-5900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>4000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>4800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1800</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,37 +1747,43 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>22700</v>
+        <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>-4100</v>
+        <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>-6700</v>
+        <v>11300</v>
       </c>
       <c r="G29" s="3">
-        <v>-6900</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
+        <v>11300</v>
+      </c>
+      <c r="H29" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="I29" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="J29" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -1679,8 +1800,14 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1853,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,46 +1906,52 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>17700</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>-8800</v>
       </c>
       <c r="G32" s="3">
-        <v>400</v>
+        <v>-8800</v>
       </c>
       <c r="H32" s="3">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-200</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-100</v>
       </c>
       <c r="L32" s="3">
         <v>-200</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
@@ -1820,55 +1959,67 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2000</v>
+        <v>-400</v>
       </c>
       <c r="E33" s="3">
-        <v>-4600</v>
+        <v>-400</v>
       </c>
       <c r="F33" s="3">
-        <v>-7500</v>
+        <v>1000</v>
       </c>
       <c r="G33" s="3">
-        <v>-7800</v>
+        <v>1000</v>
       </c>
       <c r="H33" s="3">
-        <v>-7900</v>
+        <v>-2300</v>
       </c>
       <c r="I33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="K33" s="3">
         <v>-5900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>4000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>4800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1800</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,107 +2065,125 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2000</v>
+        <v>-400</v>
       </c>
       <c r="E35" s="3">
-        <v>-4600</v>
+        <v>-400</v>
       </c>
       <c r="F35" s="3">
-        <v>-7500</v>
+        <v>1000</v>
       </c>
       <c r="G35" s="3">
-        <v>-7800</v>
+        <v>1000</v>
       </c>
       <c r="H35" s="3">
-        <v>-7900</v>
+        <v>-2300</v>
       </c>
       <c r="I35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="K35" s="3">
         <v>-5900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>4000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>4800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1800</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44377</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44196</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44012</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>43830</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43646</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2201,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,41 +2222,43 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F41" s="3">
         <v>100</v>
       </c>
-      <c r="E41" s="3">
-        <v>0</v>
-      </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
+        <v>100</v>
+      </c>
+      <c r="H41" s="3">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3">
         <v>200</v>
       </c>
-      <c r="G41" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L41" s="3">
         <v>1700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1200</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2098,8 +2271,14 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2110,20 +2289,20 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>6700</v>
       </c>
-      <c r="G42" s="3">
-        <v>6700</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2133,11 +2312,11 @@
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -2145,41 +2324,47 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>300</v>
+      </c>
+      <c r="F43" s="3">
         <v>5400</v>
       </c>
-      <c r="E43" s="3">
-        <v>25000</v>
-      </c>
-      <c r="F43" s="3">
-        <v>14400</v>
-      </c>
       <c r="G43" s="3">
-        <v>3000</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3">
+        <v>5400</v>
+      </c>
+      <c r="H43" s="3">
+        <v>7400</v>
+      </c>
+      <c r="I43" s="3">
+        <v>7400</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3">
         <v>4200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>4800</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2192,31 +2377,37 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2239,41 +2430,47 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="E45" s="3">
-        <v>7900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>6500</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
+        <v>3000</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
+        <v>25600</v>
+      </c>
+      <c r="I45" s="3">
+        <v>25600</v>
       </c>
       <c r="J45" s="3">
+        <v>20500</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>1400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2286,41 +2483,47 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>34100</v>
+      </c>
+      <c r="F46" s="3">
         <v>5500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
+        <v>5500</v>
+      </c>
+      <c r="H46" s="3">
         <v>32900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
+        <v>32900</v>
+      </c>
+      <c r="J46" s="3">
         <v>27400</v>
       </c>
-      <c r="G46" s="3">
-        <v>12300</v>
-      </c>
-      <c r="H46" s="3">
-        <v>20400</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>27100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>7300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>6100</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2333,31 +2536,37 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2380,8 +2589,14 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2391,11 +2606,11 @@
       <c r="E48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F48" s="3">
-        <v>200</v>
-      </c>
-      <c r="G48" s="3">
-        <v>300</v>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
@@ -2403,18 +2618,18 @@
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L48" s="3">
         <v>2200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2000</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2427,41 +2642,47 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>3</v>
+      <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
       </c>
       <c r="F49" s="3">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="G49" s="3">
-        <v>5900</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
       </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L49" s="3">
         <v>5200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>2900</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2474,8 +2695,14 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2748,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,41 +2801,47 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>28500</v>
+      </c>
+      <c r="F52" s="3">
         <v>52200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
+        <v>52200</v>
+      </c>
+      <c r="H52" s="3">
         <v>200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="I52" s="3">
+        <v>200</v>
+      </c>
+      <c r="J52" s="3">
         <v>3300</v>
       </c>
-      <c r="G52" s="3">
-        <v>200</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3">
         <v>1200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1000</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2615,8 +2854,14 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,41 +2907,47 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>62600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>62600</v>
+      </c>
+      <c r="F54" s="3">
         <v>57700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
+        <v>57700</v>
+      </c>
+      <c r="H54" s="3">
         <v>33100</v>
-      </c>
-      <c r="F54" s="3">
-        <v>30600</v>
-      </c>
-      <c r="G54" s="3">
-        <v>18700</v>
-      </c>
-      <c r="H54" s="3">
-        <v>28500</v>
       </c>
       <c r="I54" s="3">
         <v>33100</v>
       </c>
       <c r="J54" s="3">
+        <v>30600</v>
+      </c>
+      <c r="K54" s="3">
+        <v>33100</v>
+      </c>
+      <c r="L54" s="3">
         <v>16000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>12000</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2709,8 +2960,14 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2985,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,22 +3006,24 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>100</v>
+      <c r="D57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F57" s="3">
-        <v>3200</v>
-      </c>
-      <c r="G57" s="3">
-        <v>3300</v>
+      <c r="F57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
@@ -2770,18 +3031,18 @@
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3">
         <v>600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>600</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2794,41 +3055,47 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>3600</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L58" s="3">
         <v>3100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2800</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2841,41 +3108,47 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E59" s="3">
+        <v>100</v>
+      </c>
+      <c r="F59" s="3">
+        <v>100</v>
+      </c>
+      <c r="G59" s="3">
+        <v>100</v>
+      </c>
+      <c r="H59" s="3">
         <v>24300</v>
       </c>
-      <c r="F59" s="3">
-        <v>26800</v>
-      </c>
-      <c r="G59" s="3">
-        <v>3700</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
+      <c r="I59" s="3">
+        <v>24300</v>
       </c>
       <c r="J59" s="3">
+        <v>24300</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3">
         <v>3900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>3200</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2888,8 +3161,14 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2897,32 +3176,32 @@
         <v>100</v>
       </c>
       <c r="E60" s="3">
+        <v>100</v>
+      </c>
+      <c r="F60" s="3">
+        <v>100</v>
+      </c>
+      <c r="G60" s="3">
+        <v>100</v>
+      </c>
+      <c r="H60" s="3">
         <v>24300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="I60" s="3">
+        <v>24300</v>
+      </c>
+      <c r="J60" s="3">
         <v>24100</v>
       </c>
-      <c r="G60" s="3">
-        <v>10600</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L60" s="3">
         <v>7500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>6600</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2935,8 +3214,14 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2950,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2982,41 +3267,47 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3">
         <v>2200</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
+      <c r="I62" s="3">
+        <v>2200</v>
       </c>
       <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>300</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3029,8 +3320,14 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3373,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3426,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,8 +3479,14 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -3179,32 +3494,32 @@
         <v>100</v>
       </c>
       <c r="E66" s="3">
-        <v>26100</v>
+        <v>100</v>
       </c>
       <c r="F66" s="3">
+        <v>100</v>
+      </c>
+      <c r="G66" s="3">
+        <v>100</v>
+      </c>
+      <c r="H66" s="3">
+        <v>26500</v>
+      </c>
+      <c r="I66" s="3">
+        <v>26500</v>
+      </c>
+      <c r="J66" s="3">
         <v>24100</v>
       </c>
-      <c r="G66" s="3">
-        <v>11500</v>
-      </c>
-      <c r="H66" s="3">
-        <v>13400</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>11000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>8100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>7100</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3217,8 +3532,14 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3557,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3606,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3659,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3377,8 +3712,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,41 +3765,47 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-24600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="H72" s="3">
         <v>-32200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="I72" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="J72" s="3">
         <v>-27600</v>
       </c>
-      <c r="G72" s="3">
-        <v>-20100</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L72" s="3">
         <v>1500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-1000</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3471,8 +3818,14 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3871,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3924,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,41 +3977,47 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>62500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>62500</v>
+      </c>
+      <c r="F76" s="3">
         <v>57600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
+        <v>57600</v>
+      </c>
+      <c r="H76" s="3">
         <v>6900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
+        <v>6900</v>
+      </c>
+      <c r="J76" s="3">
         <v>6600</v>
       </c>
-      <c r="G76" s="3">
-        <v>7200</v>
-      </c>
-      <c r="H76" s="3">
-        <v>15100</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>22200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>7900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>4900</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3659,8 +4030,14 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,107 +4083,125 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44377</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44196</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44012</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>43830</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43646</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2000</v>
+        <v>-400</v>
       </c>
       <c r="E81" s="3">
-        <v>-4600</v>
+        <v>-400</v>
       </c>
       <c r="F81" s="3">
-        <v>-7500</v>
+        <v>1000</v>
       </c>
       <c r="G81" s="3">
-        <v>-7800</v>
+        <v>1000</v>
       </c>
       <c r="H81" s="3">
-        <v>-7900</v>
+        <v>-2300</v>
       </c>
       <c r="I81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="K81" s="3">
         <v>-5900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>4000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>4800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1800</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,8 +4219,10 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3835,11 +4232,11 @@
       <c r="E83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F83" s="3">
-        <v>800</v>
-      </c>
-      <c r="G83" s="3">
-        <v>600</v>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
@@ -3848,17 +4245,17 @@
         <v>3</v>
       </c>
       <c r="J83" s="3">
+        <v>100</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3">
         <v>500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>200</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3871,8 +4268,14 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4321,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4374,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4427,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4480,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,41 +4533,47 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-300</v>
+        <v>700</v>
       </c>
       <c r="E89" s="3">
-        <v>-2500</v>
+        <v>700</v>
       </c>
       <c r="F89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H89" s="3">
         <v>-1200</v>
       </c>
-      <c r="G89" s="3">
-        <v>-4000</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
+      <c r="I89" s="3">
+        <v>-1200</v>
       </c>
       <c r="J89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3">
         <v>1500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1200</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4153,8 +4586,14 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,31 +4611,33 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-500</v>
+        <v>-400</v>
       </c>
       <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+        <v>-400</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -4207,11 +4648,11 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
@@ -4219,8 +4660,14 @@
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4713,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,41 +4766,47 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-45400</v>
+        <v>-500</v>
       </c>
       <c r="E94" s="3">
-        <v>-2000</v>
+        <v>-500</v>
       </c>
       <c r="F94" s="3">
-        <v>-5300</v>
+        <v>-22700</v>
       </c>
       <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
+        <v>-22700</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-1000</v>
       </c>
       <c r="J94" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3">
         <v>-3200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-900</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4360,8 +4819,14 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,31 +4844,33 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4426,8 +4893,14 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4946,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4999,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,41 +5052,47 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>45700</v>
+        <v>2800</v>
       </c>
       <c r="E100" s="3">
-        <v>3800</v>
+        <v>2800</v>
       </c>
       <c r="F100" s="3">
-        <v>6300</v>
+        <v>22900</v>
       </c>
       <c r="G100" s="3">
-        <v>-700</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
+        <v>22900</v>
+      </c>
+      <c r="H100" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I100" s="3">
+        <v>1900</v>
       </c>
       <c r="J100" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
         <v>-200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4614,13 +5105,19 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="E101" s="3">
         <v>100</v>
@@ -4631,23 +5128,23 @@
       <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
+      <c r="H101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-100</v>
       </c>
       <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
+        <v>100</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
@@ -4661,41 +5158,47 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-100</v>
+        <v>3100</v>
       </c>
       <c r="E102" s="3">
-        <v>-500</v>
+        <v>3100</v>
       </c>
       <c r="F102" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-200</v>
       </c>
       <c r="J102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3">
         <v>-1800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-2300</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4706,6 +5209,12 @@
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IFBD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IFBD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="92">
   <si>
     <t>IFBD</t>
   </si>
@@ -656,250 +656,275 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44196</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44012</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43830</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43646</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>700</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
         <v>100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>100</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3">
         <v>4500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>14500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>6200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>18200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>9400</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E9" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
         <v>100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>100</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3">
         <v>3700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>4700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>2200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>8000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>4600</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E10" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
         <v>100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>100</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3">
         <v>800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>9800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>4000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>10200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>4800</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -919,16 +944,18 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>3</v>
@@ -945,35 +972,41 @@
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3">
         <v>1700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>1200</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,8 +1058,14 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1051,15 +1090,15 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>2400</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1072,14 +1111,20 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1090,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>100</v>
@@ -1102,14 +1147,14 @@
         <v>100</v>
       </c>
       <c r="J15" s="3">
+        <v>100</v>
+      </c>
+      <c r="K15" s="3">
+        <v>100</v>
+      </c>
+      <c r="L15" s="3">
         <v>200</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1131,8 +1176,14 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1200,128 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F17" s="3">
         <v>400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>10900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>10200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>4500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>12200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>7100</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-6400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>4300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>6000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>2300</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,8 +1341,10 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1288,40 +1355,40 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>8800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>8800</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>200</v>
-      </c>
-      <c r="L20" s="3">
-        <v>200</v>
-      </c>
-      <c r="M20" s="3">
-        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>200</v>
       </c>
       <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="P20" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
@@ -1329,8 +1396,14 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1341,163 +1414,181 @@
         <v>-400</v>
       </c>
       <c r="F21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H21" s="3">
         <v>-9800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-9800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-200</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>5000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>2000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>6400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>2400</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="D22" s="3">
+        <v>300</v>
+      </c>
+      <c r="E22" s="3">
+        <v>300</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
         <v>400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>400</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
         <v>600</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3">
         <v>200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>300</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-10300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-10300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-6200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>4300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>5800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>2000</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>3</v>
@@ -1514,26 +1605,26 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>300</v>
-      </c>
-      <c r="M24" s="3">
-        <v>100</v>
-      </c>
-      <c r="N24" s="3">
-        <v>700</v>
       </c>
       <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
+      <c r="P24" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>100</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
@@ -1541,8 +1632,14 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1691,132 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-10300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-10300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-6300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>4100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>5100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>2000</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F27" s="3">
         <v>-400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>1000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>1000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-2300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-2300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-3800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-5900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>4000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>4800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>1800</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,8 +1868,14 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1765,31 +1886,31 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>11300</v>
       </c>
-      <c r="G29" s="3">
+      <c r="I29" s="3">
         <v>11300</v>
       </c>
-      <c r="H29" s="3">
+      <c r="J29" s="3">
         <v>-2100</v>
       </c>
-      <c r="I29" s="3">
+      <c r="K29" s="3">
         <v>-2100</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>-3400</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -1806,8 +1927,14 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1986,14 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,8 +2045,14 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1924,40 +2063,40 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-8800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-8800</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-200</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>-200</v>
       </c>
       <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
@@ -1965,61 +2104,73 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F33" s="3">
         <v>-400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>1000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>1000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-2300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-3800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-5900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>4000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>4800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>1800</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2222,137 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F35" s="3">
         <v>-400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>1000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>1000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-2300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-3800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-5900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>4000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>4800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>1800</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44196</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44012</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43830</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43646</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2372,10 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,47 +2395,49 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F41" s="3">
         <v>6200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>6200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>100</v>
       </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
-      <c r="I41" s="3">
-        <v>0</v>
-      </c>
       <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3">
         <v>200</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3">
         <v>1700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1200</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2277,8 +2450,14 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2301,14 +2480,14 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>6700</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2318,11 +2497,11 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -2330,47 +2509,53 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F43" s="3">
         <v>300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>5400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>5400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>7400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>7400</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3">
         <v>4200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>4800</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2383,8 +2568,14 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2409,11 +2600,11 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2436,47 +2627,53 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>3000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>3000</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>25600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>25600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>20500</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>1400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2489,47 +2686,53 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F46" s="3">
         <v>34100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>34100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>5500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>5500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>32900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>32900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>27400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>27100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>7300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>6100</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2542,8 +2745,14 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2568,11 +2777,11 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2595,16 +2804,22 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>3</v>
+      <c r="D48" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1300</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>3</v>
@@ -2624,18 +2839,18 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3">
         <v>2200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2000</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2648,16 +2863,22 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>62400</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>62400</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
@@ -2674,21 +2895,21 @@
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3">
         <v>5200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>2900</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2701,8 +2922,14 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2981,14 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,47 +3040,53 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3">
         <v>28500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>28500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>52200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>52200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>3300</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3">
         <v>1200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1000</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2860,8 +3099,14 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,47 +3158,53 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>73800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>73800</v>
+      </c>
+      <c r="F54" s="3">
         <v>62600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>62600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>57700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>57700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>33100</v>
-      </c>
-      <c r="I54" s="3">
-        <v>33100</v>
-      </c>
-      <c r="J54" s="3">
-        <v>30600</v>
       </c>
       <c r="K54" s="3">
         <v>33100</v>
       </c>
       <c r="L54" s="3">
+        <v>30600</v>
+      </c>
+      <c r="M54" s="3">
+        <v>33100</v>
+      </c>
+      <c r="N54" s="3">
         <v>16000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>12000</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2966,8 +3217,14 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3244,10 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,16 +3267,18 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>3</v>
+      <c r="D57" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2800</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>3</v>
@@ -3037,18 +3298,18 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3">
         <v>600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>600</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3061,16 +3322,22 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -3087,21 +3354,21 @@
       <c r="J58" s="3">
         <v>0</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3">
         <v>3100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>2800</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3114,16 +3381,22 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E59" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F59" s="3">
         <v>100</v>
@@ -3132,29 +3405,29 @@
         <v>100</v>
       </c>
       <c r="H59" s="3">
-        <v>24300</v>
+        <v>100</v>
       </c>
       <c r="I59" s="3">
-        <v>24300</v>
+        <v>100</v>
       </c>
       <c r="J59" s="3">
         <v>24300</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
+      <c r="K59" s="3">
+        <v>24300</v>
       </c>
       <c r="L59" s="3">
+        <v>24300</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>3900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>3200</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3167,16 +3440,22 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>100</v>
+        <v>3800</v>
       </c>
       <c r="E60" s="3">
-        <v>100</v>
+        <v>3800</v>
       </c>
       <c r="F60" s="3">
         <v>100</v>
@@ -3185,29 +3464,29 @@
         <v>100</v>
       </c>
       <c r="H60" s="3">
+        <v>100</v>
+      </c>
+      <c r="I60" s="3">
+        <v>100</v>
+      </c>
+      <c r="J60" s="3">
         <v>24300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>24300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>24100</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3">
         <v>7500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>6600</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3220,16 +3499,22 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -3273,16 +3558,22 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
+      <c r="D62" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2900</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
@@ -3290,30 +3581,30 @@
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3">
         <v>2200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>2200</v>
       </c>
-      <c r="J62" s="3">
-        <v>0</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
         <v>300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>300</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3326,8 +3617,14 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3676,14 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3735,14 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,16 +3794,22 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>100</v>
+        <v>7000</v>
       </c>
       <c r="E66" s="3">
-        <v>100</v>
+        <v>7000</v>
       </c>
       <c r="F66" s="3">
         <v>100</v>
@@ -3503,29 +3818,29 @@
         <v>100</v>
       </c>
       <c r="H66" s="3">
+        <v>100</v>
+      </c>
+      <c r="I66" s="3">
+        <v>100</v>
+      </c>
+      <c r="J66" s="3">
         <v>26500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>26500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>24100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>11000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>8100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>7100</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3538,8 +3853,14 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3880,10 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3935,14 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +3994,14 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3718,8 +4053,14 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,47 +4112,53 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-26700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-26700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-25400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-25400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-24600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-24600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-32200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-32200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-27600</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3">
         <v>1500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-1000</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3824,8 +4171,14 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4230,14 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4289,14 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,47 +4348,53 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>64800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>64800</v>
+      </c>
+      <c r="F76" s="3">
         <v>62500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>62500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>57600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>57600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>6900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>6900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>6600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>22200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>7900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>4900</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4036,8 +4407,14 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4466,137 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44196</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44012</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43830</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43646</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F81" s="3">
         <v>-400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>1000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>1000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-2300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-3800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-5900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>4000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>4800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>1800</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,8 +4616,10 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4244,24 +4641,24 @@
       <c r="I83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3">
         <v>500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>200</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4274,8 +4671,14 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4730,14 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4789,14 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4848,14 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4907,14 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,47 +4966,53 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F89" s="3">
         <v>700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-600</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3">
         <v>1500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1200</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4592,8 +5025,14 @@
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,23 +5052,25 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-400</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4639,11 +5080,11 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -4654,11 +5095,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
@@ -4666,8 +5107,14 @@
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +5166,14 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,47 +5225,53 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-22700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-22700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-1000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-2600</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3">
         <v>-3200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-900</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4825,8 +5284,14 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,8 +5311,10 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4872,11 +5339,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4899,8 +5366,14 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5425,14 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5484,14 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,47 +5543,53 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F100" s="3">
         <v>2800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>2800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>22900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>22900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>1900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>1900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>3100</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>-200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5111,22 +5602,28 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-100</v>
       </c>
       <c r="H101" s="3">
         <v>-100</v>
@@ -5135,22 +5632,22 @@
         <v>-100</v>
       </c>
       <c r="J101" s="3">
-        <v>100</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="K101" s="3">
+        <v>-100</v>
       </c>
       <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3">
+        <v>100</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
@@ -5164,47 +5661,53 @@
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F102" s="3">
         <v>3100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>3100</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="I102" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3">
         <v>-200</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
+      <c r="K102" s="3">
+        <v>-200</v>
       </c>
       <c r="L102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3">
         <v>-1800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-2300</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5215,6 +5718,12 @@
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/IFBD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IFBD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="92">
   <si>
     <t>IFBD</t>
   </si>
@@ -2638,11 +2638,11 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>200</v>
       </c>
       <c r="F45" s="3">
         <v>3000</v>
@@ -2650,11 +2650,11 @@
       <c r="G45" s="3">
         <v>3000</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
+      <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
+        <v>0</v>
       </c>
       <c r="J45" s="3">
         <v>25600</v>
@@ -4978,10 +4978,10 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-2800</v>
+        <v>1000</v>
       </c>
       <c r="E89" s="3">
-        <v>-2800</v>
+        <v>1000</v>
       </c>
       <c r="F89" s="3">
         <v>700</v>
@@ -5237,10 +5237,10 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-1700</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>-1700</v>
       </c>
       <c r="F94" s="3">
         <v>-500</v>
@@ -5555,10 +5555,10 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="E100" s="3">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="F100" s="3">
         <v>2800</v>

--- a/AAII_Financials/Quarterly/IFBD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IFBD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="92">
   <si>
     <t>IFBD</t>
   </si>
@@ -656,236 +656,255 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F8" s="3">
         <v>1700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>700</v>
       </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
       <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
         <v>100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>100</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3">
         <v>4500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>14500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>6200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>18200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>9400</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F9" s="3">
         <v>1100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>400</v>
       </c>
-      <c r="H9" s="3">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
       <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
         <v>100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>100</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3">
         <v>3700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>4700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>2200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>8000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>4600</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -896,61 +915,67 @@
         <v>600</v>
       </c>
       <c r="F10" s="3">
+        <v>600</v>
+      </c>
+      <c r="G10" s="3">
+        <v>600</v>
+      </c>
+      <c r="H10" s="3">
         <v>300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>300</v>
       </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
       <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
         <v>100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>100</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3">
         <v>800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>9800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>4000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>10200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>4800</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -974,28 +999,30 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
@@ -1012,35 +1039,41 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3">
         <v>1700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>1900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>1200</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,16 +1137,22 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E14" s="3">
+        <v>27400</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1142,15 +1181,15 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>2400</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1163,14 +1202,20 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1193,10 +1238,10 @@
         <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3">
         <v>100</v>
@@ -1205,14 +1250,14 @@
         <v>100</v>
       </c>
       <c r="N15" s="3">
+        <v>100</v>
+      </c>
+      <c r="O15" s="3">
+        <v>100</v>
+      </c>
+      <c r="P15" s="3">
         <v>200</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1234,8 +1279,14 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,81 +1307,89 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F17" s="3">
         <v>2300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>10900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>10200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>4500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>12200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>7100</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-500</v>
+        <v>-300</v>
       </c>
       <c r="E18" s="3">
-        <v>-500</v>
+        <v>-300</v>
       </c>
       <c r="F18" s="3">
         <v>-500</v>
@@ -1339,55 +1398,61 @@
         <v>-500</v>
       </c>
       <c r="H18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J18" s="3">
         <v>-400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-1200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-6400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>4300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>1700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>6000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>2300</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,16 +1476,18 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1435,40 +1502,40 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>8800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>8800</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>200</v>
-      </c>
-      <c r="P20" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>100</v>
       </c>
       <c r="R20" s="3">
         <v>200</v>
       </c>
       <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="T20" s="3">
+        <v>200</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
@@ -1476,22 +1543,28 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-500</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-400</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-400</v>
       </c>
       <c r="H21" s="3">
         <v>-400</v>
@@ -1500,57 +1573,63 @@
         <v>-400</v>
       </c>
       <c r="J21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L21" s="3">
         <v>-9800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-9800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-200</v>
       </c>
-      <c r="N21" s="3">
-        <v>0</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>5000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>2000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>6400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>2400</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E22" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F22" s="3">
         <v>300</v>
@@ -1558,121 +1637,133 @@
       <c r="G22" s="3">
         <v>300</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="H22" s="3">
+        <v>300</v>
+      </c>
+      <c r="I22" s="3">
+        <v>300</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
         <v>400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>400</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3">
         <v>600</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3">
         <v>200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>300</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="F23" s="3">
         <v>-800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-10300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-10300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-6200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>4300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>1700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>5800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>2000</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1688,11 +1779,11 @@
       <c r="G24" s="3">
         <v>0</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
@@ -1709,26 +1800,26 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>300</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>100</v>
-      </c>
-      <c r="R24" s="3">
-        <v>700</v>
       </c>
       <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
+      <c r="T24" s="3">
+        <v>700</v>
+      </c>
+      <c r="U24" s="3">
+        <v>100</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
@@ -1736,8 +1827,14 @@
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1898,156 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="F26" s="3">
         <v>-800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-10300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-10300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-6300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>4100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>1600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>5100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>2000</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="F27" s="3">
         <v>-800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>1000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-2300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-3800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-5900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>4000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>1500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>4800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>1800</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2111,14 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2020,31 +2141,31 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>11300</v>
       </c>
-      <c r="K29" s="3">
+      <c r="M29" s="3">
         <v>11300</v>
       </c>
-      <c r="L29" s="3">
+      <c r="N29" s="3">
         <v>-2100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="O29" s="3">
         <v>-2100</v>
       </c>
-      <c r="N29" s="3">
+      <c r="P29" s="3">
         <v>-3400</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2061,8 +2182,14 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2253,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,16 +2324,22 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -2215,40 +2354,40 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-8800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-8800</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-200</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-100</v>
       </c>
       <c r="R32" s="3">
         <v>-200</v>
       </c>
       <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="T32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
@@ -2256,73 +2395,85 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="F33" s="3">
         <v>-800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>1000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-2300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-2300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-3800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-5900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>4000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>1500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>4800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>1800</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2537,161 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="F35" s="3">
         <v>-800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>1000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-2300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-2300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-3800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-5900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>4000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>1500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>4800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>1800</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2715,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,59 +2742,61 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F41" s="3">
         <v>5200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>5200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>6200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>6200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>100</v>
       </c>
-      <c r="L41" s="3">
-        <v>0</v>
-      </c>
-      <c r="M41" s="3">
-        <v>0</v>
-      </c>
       <c r="N41" s="3">
+        <v>0</v>
+      </c>
+      <c r="O41" s="3">
+        <v>0</v>
+      </c>
+      <c r="P41" s="3">
         <v>200</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3">
         <v>1700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1200</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2636,23 +2809,29 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>700</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -2672,14 +2851,14 @@
         <v>0</v>
       </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>6700</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2689,11 +2868,11 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
-      </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -2701,59 +2880,65 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F43" s="3">
         <v>2600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>5200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>5200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>5400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>5400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>7400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>7400</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P43" s="3">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3">
         <v>4200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>4800</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2766,8 +2951,14 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2804,11 +2995,11 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2831,8 +3022,14 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2849,41 +3046,41 @@
         <v>200</v>
       </c>
       <c r="H45" s="3">
+        <v>200</v>
+      </c>
+      <c r="I45" s="3">
+        <v>200</v>
+      </c>
+      <c r="J45" s="3">
         <v>3000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>3000</v>
       </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
         <v>25600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>25600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>20500</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3">
         <v>1400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>100</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2896,59 +3093,65 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>9600</v>
+      </c>
+      <c r="F46" s="3">
         <v>8700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>8700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>10000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>10000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>34100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>34100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>5500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>5500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>32900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>32900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>27400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>27100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>7300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>6100</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2961,8 +3164,14 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2999,11 +3208,11 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3026,29 +3235,35 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F48" s="3">
         <v>1200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1300</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3067,18 +3282,18 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3">
         <v>2200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>2000</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3091,16 +3306,22 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>62400</v>
+        <v>12600</v>
       </c>
       <c r="E49" s="3">
-        <v>62400</v>
+        <v>12600</v>
       </c>
       <c r="F49" s="3">
         <v>62400</v>
@@ -3109,10 +3330,10 @@
         <v>62400</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>62400</v>
       </c>
       <c r="I49" s="3">
-        <v>0</v>
+        <v>62400</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
@@ -3129,21 +3350,21 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
+      <c r="O49" s="3">
+        <v>0</v>
       </c>
       <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3">
         <v>5200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>2900</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3156,8 +3377,14 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3448,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,8 +3519,14 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3303,42 +3542,42 @@
       <c r="G52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3">
         <v>28500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>28500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>52200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>52200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>3300</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3">
         <v>1200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>1000</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,8 +3590,14 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,59 +3661,65 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>23200</v>
+      </c>
+      <c r="F54" s="3">
         <v>72400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>72400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>73800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>73800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>62600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>62600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>57700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>57700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>33100</v>
-      </c>
-      <c r="M54" s="3">
-        <v>33100</v>
-      </c>
-      <c r="N54" s="3">
-        <v>30600</v>
       </c>
       <c r="O54" s="3">
         <v>33100</v>
       </c>
       <c r="P54" s="3">
+        <v>30600</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>33100</v>
+      </c>
+      <c r="R54" s="3">
         <v>16000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>12000</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3481,8 +3732,14 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3763,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,29 +3790,31 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F57" s="3">
         <v>2600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2800</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3572,18 +3833,18 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3">
         <v>600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>600</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3596,16 +3857,22 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="E58" s="3">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="F58" s="3">
         <v>200</v>
@@ -3614,10 +3881,10 @@
         <v>200</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -3634,21 +3901,21 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
+      <c r="O58" s="3">
+        <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3">
         <v>3100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>2800</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3661,8 +3928,14 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3673,16 +3946,16 @@
         <v>300</v>
       </c>
       <c r="F59" s="3">
+        <v>300</v>
+      </c>
+      <c r="G59" s="3">
+        <v>300</v>
+      </c>
+      <c r="H59" s="3">
         <v>500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>500</v>
-      </c>
-      <c r="H59" s="3">
-        <v>100</v>
-      </c>
-      <c r="I59" s="3">
-        <v>100</v>
       </c>
       <c r="J59" s="3">
         <v>100</v>
@@ -3691,29 +3964,29 @@
         <v>100</v>
       </c>
       <c r="L59" s="3">
-        <v>24300</v>
+        <v>100</v>
       </c>
       <c r="M59" s="3">
-        <v>24300</v>
+        <v>100</v>
       </c>
       <c r="N59" s="3">
         <v>24300</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
+      <c r="O59" s="3">
+        <v>24300</v>
       </c>
       <c r="P59" s="3">
+        <v>24300</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3">
         <v>3900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>3200</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3726,28 +3999,34 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F60" s="3">
         <v>3400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3800</v>
-      </c>
-      <c r="H60" s="3">
-        <v>100</v>
-      </c>
-      <c r="I60" s="3">
-        <v>100</v>
       </c>
       <c r="J60" s="3">
         <v>100</v>
@@ -3756,29 +4035,29 @@
         <v>100</v>
       </c>
       <c r="L60" s="3">
+        <v>100</v>
+      </c>
+      <c r="M60" s="3">
+        <v>100</v>
+      </c>
+      <c r="N60" s="3">
         <v>24300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>24300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>24100</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3">
         <v>7500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>6600</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3791,29 +4070,35 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>100</v>
+      </c>
+      <c r="E61" s="3">
+        <v>100</v>
+      </c>
+      <c r="F61" s="3">
         <v>200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>300</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -3856,8 +4141,14 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3867,48 +4158,48 @@
       <c r="E62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3">
         <v>2900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>2900</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
         <v>2200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>2200</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3">
         <v>300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>300</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3921,8 +4212,14 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4283,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4354,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,28 +4425,34 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F66" s="3">
         <v>3700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>3700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>7000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>7000</v>
-      </c>
-      <c r="H66" s="3">
-        <v>100</v>
-      </c>
-      <c r="I66" s="3">
-        <v>100</v>
       </c>
       <c r="J66" s="3">
         <v>100</v>
@@ -4146,29 +4461,29 @@
         <v>100</v>
       </c>
       <c r="L66" s="3">
+        <v>100</v>
+      </c>
+      <c r="M66" s="3">
+        <v>100</v>
+      </c>
+      <c r="N66" s="3">
         <v>26500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>26500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>24100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>11000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>8100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>7100</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4181,8 +4496,14 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4527,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4594,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4665,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4401,8 +4736,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,59 +4807,65 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-83900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-83900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-28300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-28300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-26700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-26700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-25400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-25400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-24600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-24600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-32200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-32200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-27600</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3">
         <v>1500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-1000</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4531,8 +4878,14 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4949,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +5020,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,59 +5091,65 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F76" s="3">
         <v>66700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>66700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>64800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>64800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>62500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>62500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>57600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>57600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>6900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>6900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>6600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>22200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>7900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>4900</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4791,8 +5162,14 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5233,161 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="F81" s="3">
         <v>-800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>1000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-2300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-2300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-3800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-5900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>4000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>1500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>4800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>1800</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,16 +5411,18 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>100</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>3</v>
@@ -5051,24 +5448,24 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3">
         <v>100</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3">
         <v>500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>200</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5081,8 +5478,14 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5549,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5620,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5691,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5762,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,59 +5833,65 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F89" s="3">
         <v>600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>600</v>
       </c>
-      <c r="F89" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G89" s="3">
-        <v>1000</v>
-      </c>
       <c r="H89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J89" s="3">
         <v>2200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>2200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-600</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3">
         <v>1500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-1200</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5471,8 +5904,14 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,8 +5935,10 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5507,24 +5948,24 @@
       <c r="E91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5534,11 +5975,11 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -5549,11 +5990,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
@@ -5561,8 +6002,14 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +6073,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,59 +6144,65 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="F94" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-1700</v>
-      </c>
       <c r="H94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J94" s="3">
         <v>-2000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-2000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-22700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-22700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-2600</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-900</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5756,8 +6215,14 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6246,10 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5819,11 +6286,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5846,8 +6313,14 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6384,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6455,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,59 +6526,65 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
+      <c r="D100" s="3">
+        <v>300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>300</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>2800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>2800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>22900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>22900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>1900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>1900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>3100</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3">
         <v>-200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6106,8 +6597,14 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6118,22 +6615,22 @@
         <v>0</v>
       </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>100</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-100</v>
       </c>
       <c r="L101" s="3">
         <v>-100</v>
@@ -6142,22 +6639,22 @@
         <v>-100</v>
       </c>
       <c r="N101" s="3">
-        <v>100</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-100</v>
       </c>
       <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3">
+        <v>100</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
@@ -6171,59 +6668,65 @@
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F102" s="3">
         <v>300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>3100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>3100</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="M102" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="N102" s="3">
         <v>-200</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
+      <c r="O102" s="3">
+        <v>-200</v>
       </c>
       <c r="P102" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-2300</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6234,6 +6737,12 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
